--- a/docs/Project_Requirements.xlsx
+++ b/docs/Project_Requirements.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{372AEAF1-2658-4EE7-BA4B-4E467E90C408}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3542859E-845A-4D80-8F56-35F70AF2035B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{D8ADA236-363B-4564-8A01-96EAD65C3C5F}"/>
   </bookViews>
@@ -1959,7 +1959,7 @@
       </c>
       <c r="C5" s="28">
         <f ca="1">TODAY()</f>
-        <v>46168</v>
+        <v>46173</v>
       </c>
       <c r="D5" s="27"/>
       <c r="E5" s="20"/>
@@ -3286,7 +3286,7 @@
         <v>109</v>
       </c>
       <c r="E53" s="32" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="F53" s="32" t="s">
         <v>253</v>
